--- a/GameConfig/Datas/新手引导配置表.xlsx
+++ b/GameConfig/Datas/新手引导配置表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub_Project\DGame\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58EC380C-8A77-4326-B668-128669164FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993EC9B8-2348-408C-9EFB-B4B4FCD6AFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2590" windowWidth="28800" windowHeight="15380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="新手引导组配置表" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="118">
   <si>
     <t>##var</t>
   </si>
@@ -397,10 +397,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DoNotResume</t>
-  </si>
-  <si>
     <t>Group</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EGuideType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuideType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>引导类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ForceGuide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeakGuide</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuideTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>引导时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -505,13 +530,13 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -986,8 +1011,8 @@
       <c r="H5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>110</v>
+      <c r="I5" s="2">
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>65</v>
@@ -1004,7 +1029,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AH7"/>
+  <dimension ref="A1:AJ7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="2" customWidth="1"/>
@@ -1018,24 +1043,24 @@
     <col min="9" max="9" width="17.90625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.36328125" style="2" customWidth="1"/>
     <col min="11" max="11" width="13.90625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="20.26953125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="21.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="19" width="22.08984375" style="2" customWidth="1"/>
-    <col min="20" max="20" width="16.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="26.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="26.81640625" style="2" customWidth="1"/>
+    <col min="12" max="14" width="20.26953125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="21.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="22.08984375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="16.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="26.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="27" width="22.08984375" style="2" customWidth="1"/>
-    <col min="28" max="28" width="11.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="24.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="33" width="24.54296875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="24.81640625" style="2" customWidth="1"/>
-    <col min="35" max="36" width="8.7265625" style="2" customWidth="1"/>
-    <col min="37" max="16384" width="8.7265625" style="2"/>
+    <col min="24" max="24" width="26.81640625" style="2" customWidth="1"/>
+    <col min="25" max="25" width="26.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="29" width="22.08984375" style="2" customWidth="1"/>
+    <col min="30" max="30" width="11.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="24.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="35" width="24.54296875" style="2" customWidth="1"/>
+    <col min="36" max="36" width="24.81640625" style="2" customWidth="1"/>
+    <col min="37" max="38" width="8.7265625" style="2" customWidth="1"/>
+    <col min="39" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1057,11 +1082,11 @@
       <c r="G1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
       <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
@@ -1069,61 +1094,67 @@
         <v>6</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="Q1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="10" t="s">
+      <c r="R1" s="10"/>
+      <c r="S1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="9"/>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="10"/>
+      <c r="U1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="X1" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10" t="s">
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AD1" s="10" t="s">
+      <c r="AF1" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="AE1" s="10"/>
-      <c r="AF1" s="10" t="s">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="AG1" s="10"/>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="8"/>
+      <c r="AJ1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
@@ -1145,11 +1176,11 @@
       <c r="G2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
       <c r="K2" s="3" t="s">
         <v>17</v>
       </c>
@@ -1157,61 +1188,67 @@
         <v>18</v>
       </c>
       <c r="M2" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="Q2" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="8" t="s">
+      <c r="R2" s="10"/>
+      <c r="S2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="R2" s="9"/>
-      <c r="S2" s="3" t="s">
+      <c r="T2" s="10"/>
+      <c r="U2" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="V2" s="8" t="s">
+      <c r="X2" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="W2" s="9"/>
-      <c r="X2" s="8" t="s">
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="3" t="s">
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="AA2" s="3" t="s">
+      <c r="AC2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="AB2" s="3" t="s">
+      <c r="AD2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="AC2" s="3" t="s">
+      <c r="AE2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AD2" s="8" t="s">
+      <c r="AF2" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AE2" s="8"/>
-      <c r="AF2" s="8" t="s">
+      <c r="AG2" s="9"/>
+      <c r="AH2" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="AG2" s="8"/>
-      <c r="AH2" s="3" t="s">
+      <c r="AI2" s="9"/>
+      <c r="AJ2" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>14</v>
       </c>
@@ -1234,52 +1271,54 @@
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
-      <c r="O3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>22</v>
-      </c>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
       <c r="Q3" s="7" t="s">
         <v>22</v>
       </c>
       <c r="R3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
+      <c r="S3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="T3" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="U3" s="7"/>
-      <c r="V3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="W3" s="7" t="s">
-        <v>22</v>
-      </c>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
       <c r="X3" s="7" t="s">
         <v>22</v>
       </c>
       <c r="Y3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7"/>
+      <c r="Z3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA3" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
-      <c r="AD3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="AE3" s="7" t="s">
-        <v>22</v>
-      </c>
+      <c r="AD3" s="7"/>
+      <c r="AE3" s="7"/>
       <c r="AF3" s="7" t="s">
         <v>22</v>
       </c>
       <c r="AG3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="AH3" s="7"/>
+      <c r="AH3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="AJ3" s="7"/>
     </row>
-    <row r="4" spans="1:34" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>24</v>
       </c>
@@ -1316,74 +1355,80 @@
       <c r="L4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="O4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="P4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="Q4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="R4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="S4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="R4" s="5" t="s">
+      <c r="T4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="S4" s="5" t="s">
+      <c r="U4" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="T4" s="5" t="s">
+      <c r="V4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="U4" s="5" t="s">
+      <c r="W4" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="V4" s="5" t="s">
+      <c r="X4" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="Y4" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="Z4" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="Y4" s="5" t="s">
+      <c r="AA4" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="Z4" s="5" t="s">
+      <c r="AB4" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="AA4" s="5" t="s">
+      <c r="AC4" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="AB4" s="5" t="s">
+      <c r="AD4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AC4" s="5" t="s">
+      <c r="AE4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="AD4" s="5" t="s">
+      <c r="AF4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="AE4" s="5" t="s">
+      <c r="AG4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AF4" s="5" t="s">
+      <c r="AH4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="AG4" s="5" t="s">
+      <c r="AI4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="AH4" s="5" t="s">
+      <c r="AJ4" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>44</v>
       </c>
@@ -1421,10 +1466,10 @@
         <v>45</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="O5" s="6" t="s">
         <v>45</v>
@@ -1439,19 +1484,19 @@
         <v>45</v>
       </c>
       <c r="S5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="T5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="U5" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="T5" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="U5" s="6" t="s">
-        <v>45</v>
-      </c>
       <c r="V5" s="6" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="W5" s="6" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="X5" s="6" t="s">
         <v>74</v>
@@ -1466,10 +1511,10 @@
         <v>74</v>
       </c>
       <c r="AB5" s="6" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="AC5" s="6" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="AD5" s="6" t="s">
         <v>45</v>
@@ -1486,8 +1531,14 @@
       <c r="AH5" s="6" t="s">
         <v>45</v>
       </c>
+      <c r="AI5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ5" s="6" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
         <v>900001</v>
       </c>
@@ -1519,76 +1570,82 @@
         <v>1</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M6" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="N6" s="2">
+        <v>5</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="O6" s="2">
-        <v>0</v>
-      </c>
-      <c r="P6" s="2">
+      <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2">
         <v>166</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="S6" s="2">
         <v>334</v>
       </c>
-      <c r="R6" s="2">
+      <c r="T6" s="2">
         <v>122</v>
       </c>
-      <c r="S6" s="2">
+      <c r="U6" s="2">
         <v>24</v>
       </c>
-      <c r="T6" s="2">
-        <v>0</v>
-      </c>
-      <c r="U6" s="2" t="s">
+      <c r="V6" s="2">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="V6" s="2">
+      <c r="X6" s="2">
         <v>200</v>
       </c>
-      <c r="W6" s="2">
+      <c r="Y6" s="2">
         <v>200</v>
       </c>
-      <c r="X6" s="2">
+      <c r="Z6" s="2">
         <v>-20</v>
       </c>
-      <c r="Y6" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="2">
+      <c r="AA6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="2">
         <v>1</v>
       </c>
-      <c r="AA6" s="2">
+      <c r="AC6" s="2">
         <v>1</v>
       </c>
-      <c r="AB6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="2" t="s">
+      <c r="AD6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AD6" s="2">
+      <c r="AF6" s="2">
         <v>100</v>
       </c>
-      <c r="AE6" s="2">
+      <c r="AG6" s="2">
         <v>200</v>
       </c>
-      <c r="AF6" s="2">
+      <c r="AH6" s="2">
         <v>300</v>
       </c>
-      <c r="AG6" s="2">
+      <c r="AI6" s="2">
         <v>100</v>
       </c>
-      <c r="AH6" s="2">
+      <c r="AJ6" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
         <v>900002</v>
       </c>
@@ -1623,38 +1680,38 @@
         <v>46</v>
       </c>
       <c r="M7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="O7" s="2">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2">
         <v>14</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>334</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>122</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>24</v>
       </c>
-      <c r="T7" s="2">
-        <v>0</v>
-      </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="V7" s="2">
-        <v>0</v>
-      </c>
-      <c r="W7" s="2">
-        <v>0</v>
-      </c>
       <c r="X7" s="2">
         <v>0</v>
       </c>
@@ -1670,15 +1727,15 @@
       <c r="AB7" s="2">
         <v>0</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AC7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AD7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="2">
-        <v>0</v>
-      </c>
       <c r="AF7" s="2">
         <v>0</v>
       </c>
@@ -1686,6 +1743,12 @@
         <v>0</v>
       </c>
       <c r="AH7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1693,18 +1756,18 @@
   <mergeCells count="14">
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="H2:J2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="Q2:R2"/>
     <mergeCell ref="AF2:AG2"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="AH2:AI2"/>
     <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="S2:T2"/>
     <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="Z2:AA2"/>
     <mergeCell ref="X1:Y1"/>
     <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="V2:W2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
